--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -1,48 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\LinkedinSummaryBot\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B181B5E2-924D-4AA8-BC9A-6FC37BEF1550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Agent_1</t>
+  </si>
+  <si>
+    <t>Agent_2</t>
+  </si>
+  <si>
+    <t>Processed</t>
+  </si>
+  <si>
+    <t>https://www.geekwire.com/2026/tech-moves-microsoft-cvp-jumps-to-google-seattle-engineers-launch-new-startup-github-names-vp/</t>
+  </si>
+  <si>
+    <t>The article "Tech Moves: Microsoft CVP jumps to Google; Seattle engineers launch new startup; GitHub names VP" highlights several significant personnel changes and new ventures in the Pacific Northwest tech community. Satish Thomas, a 20-year Microsoft veteran and corporate vice president, has moved to Google, emphasizing the current AI era's impact on tech. Raji Rajagopalan has been appointed as GitHub's vice president of engineering, aiming to foster innovation and human-agent workflows in AI-driven development. Katie Bardaro joined Avante, a Seattle startup focused on HR administration and AI-powered benefits guidance, as senior VP of customer experience. A new stealthy startup focused on AI and the workplace has been launched by Vivek Sharma, along with collaborators Tore Hanssen, Robert Masson, and Calvin Grunewald. Additionally, Jeff Carr is now CEO of Atana, a startup specializing in behavior-based workplace training. Larry Hyrb, known as "Major Nelson" from his time at Microsoft Xbox, was laid off from Unity. Jay Bartot joined TheFounderVC as a technical advisor and chief technologist. Auger, a logistics and supply chain software startup, named Tucker Reimer as principal of supply chain innovation. Finally, Lucas Dickey joined Stripe as a product builder for Stripe Atlas.</t>
+  </si>
+  <si>
+    <t>✨ PNW Tech Talent Watch: AI Fuels Executive Migration &amp; Startup Formation ✨
+The Pacific Northwest tech community is experiencing a massive talent liquidity event, driven overwhelmingly by the pursuit of cutting-edge AI opportunities. The recent shifts confirm that leaders are making big moves to shape the next era of development.
+Here is a quick breakdown of the significant transitions, illustrating where the industry is placing its bets:
+**➡️ Executive Migration Driven by AI:**
+*   **Microsoft to Google:** Satish Thomas, a 20-year Microsoft veteran and Corporate VP, has jumped to Google. This high-profile move underscores how the fierce competition in the AI space is drawing top-tier talent across legacy lines.
+*   **New Leadership at GitHub:** Raji Rajagopalan steps in as VP of Engineering, specifically tasked with innovating **human-agent workflows**—a clear strategic commitment to the future of AI-driven developer tools.
+**🚀 The Seattle Startup Boom:**
+*   A wave of new ventures is forming, focusing on highly specific, AI-enabled solutions:
+    *   **Stealth Mode AI:** Vivek Sharma, alongside Tore Hanssen, Robert Masson, and Calvin Grunewald, launched a secretive new startup focused on AI and the workplace.
+    *   **HR Tech Growth:** Avante brought on Katie Bardaro as SVP to scale its AI-powered benefits guidance and HR administration platform.
+    *   **Workplace Training Focus:** Jeff Carr is now CEO of Atana, specializing in behavior-based workplace training.
+**🔄 Strategic Moves &amp; Layoff Realities:**
+*   **The Founder's Journey:** Jay Bartot joined TheFounderVC as a Technical Advisor and Chief Technologist, signaling more seasoned experts are entering the venture capital ecosystem.
+*   **Product Building:** Lucas Dickey moved to Stripe as a Product Builder for Stripe Atlas, helping founders launch quickly.
+*   **Industry Flux:** Larry Hyrb ("Major Nelson" from Xbox fame) was laid off from Unity, a reminder that even high-profile roles face turbulence amid industry restructuring.
+**The Takeaway:**
+The theme is clear: Talent is flowing rapidly toward greenfield opportunities in AI infrastructure, developer tooling, and specialized workplace applications. The PNW is currently the epicenter for talent ready to exit large corporations to pursue these high-growth, foundational challenges.
+What do you think these migrations signal for the balance of power between Big Tech and emerging startups over the next year?
+#AIEra #TechMoves #SeattleTech #TalentWar #ExecutiveLeadership #StartupEcosystem #GitHub #Microsoft #Google #VentureCapital</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>https://www.geekwire.com/2026/vega-cloud-enters-receivership-with-millions-in-debt-in-surprise-turn-for-spokane-tech-standout/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The Spokane-area tech startup, Vega Cloud, which develops software for managing cloud spending, has entered receivership due to its inability to pay debts, including nearly $830,000 owed to Amazon Web Services. The company, founded in 2018, had raised $12.2 million and achieved approximately $7 million in annual revenue by 2023. At the time of receivership, Vega Cloud had less than $17,000 in the bank and its workforce had decreased from about 65 employees two years ago to around 35. Receivership, a state-level process, places a neutral party in charge to manage assets, pause creditor collections, and supervise asset sales and payments. The largest secured creditor is Sun Mountain Private Credit Fund I, which is owed $3.5 million, backed by Vega Cloud's intellectual property.</t>
+  </si>
+  <si>
+    <t>🚨 **A Stark Reminder: The Anatomy of a Tech Startup Receivership** 🚨
+The news concerning Spokane-based Vega Cloud, a startup specializing in cloud spending management, serves as a critical case study in the harsh reality of liquidity and debt management, even for companies showing strong revenue growth.
+Despite raising $12.2 million and achieving approximately $7 million in annual recurring revenue (ARR) by 2023, Vega Cloud has entered state-level receivership.
+Here is a factual breakdown of the situation, highlighting key operational and financial stress points:
+---
+### **Vega Cloud: The Financial Reality Check**
+| Metric | Details | Analysis |
+| :--- | :--- | :--- |
+| **Funding &amp; Revenue** | $12.2M raised; $7M ARR in 2023. | Achieved significant traction and scale. |
+| **Liquidity Crisis** | Less than $17,000 cash in the bank at filing. | Major disconnect between revenue growth and working capital. |
+| **Key Operational Debt** | Nearly $830,000 owed to Amazon Web Services (AWS). | Ironic for a company selling cloud management tools; highlights the danger of large infrastructure bills. |
+| **Secured Debt** | $3.5 million owed to Sun Mountain Private Credit Fund I. | This debt is secured by the company's Intellectual Property (IP). |
+| **Operational Decline** | Workforce reduced from ~65 employees to ~35. | Indicates severe cost-cutting measures prior to the final filing. |
+### **What Receivership Means**
+Receivership places a neutral, court-appointed party in charge of the company's assets. Its primary function is to pause creditor collections and supervise the management, sale, and distribution of assets, ultimately maximizing returns for creditors.
+### **The Takeaway for Founders &amp; Investors**
+This situation underscores a vital lesson: **Revenue is vanity; cash is sanity.** Even $7M in ARR cannot protect a company if unit economics are unstable and working capital is mismanaged. Managing the cost of goods sold (COGS)—especially major cloud infrastructure—is paramount to survival.
+A difficult but necessary reminder that growth at all costs without tight financial controls is unsustainable.
+#TechFinance #Startups #Receivership #VentureCapital #CloudCosts #FinOps #LiquidityCrisis</t>
+  </si>
+  <si>
+    <t>https://www.geekwire.com/2026/washington-lawmakers-target-addictive-social-media-feeds-in-revived-push-for-youth-safeguards/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Washington lawmakers are renewing efforts to pass legislation aimed at protecting youth from "addictive feeds" on social media platforms. House Bill 1834, supported by state Attorney General Nick Brown and Governor Bob Ferguson, seeks to prevent companies like Instagram and TikTok from providing addictive feeds to minors and restrict push notifications during certain hours without parental consent. This renewed push comes after a similar bill stalled last year due to constitutionality and privacy concerns. The tech industry, represented by groups like TechNet and NetChoice, opposes the bill, arguing it infringes on the First Amendment and that parental judgment should be prioritized. However, advocates, including former tech executives like Kelly Stonelake, who previously worked at Meta, emphasize the necessity of such regulations, citing internal knowledge of companies prioritizing engagement over youth well-being. The bill is modeled after a California law that has withstood court challenges, and proponents assert it doesn't limit access to speech but rather the addictive delivery of it.</t>
+  </si>
+  <si>
+    <t>💡 **The Battle for the Algorithm: Washington State Renews Push to Protect Youth from 'Addictive Feeds'**
+The debate over social media regulation is intensifying in Washington State as lawmakers revive efforts to pass House Bill 1834. This legislation, championed by Governor Bob Ferguson and Attorney General Nick Brown, aims to impose strict limits on how social media companies deliver content to minors, signaling a potential shift in platform accountability.
+This isn't just about limiting screen time; it's about regulating the core mechanisms of addiction built into the platforms themselves.
+### HB 1834: Key Provisions &amp; Conflict Points
+The proposed bill directly targets practices critics argue prioritize engagement metrics over youth well-being:
+*   **🚫 Banning Addictive Feeds:** Prohibiting platforms like Instagram and TikTok from providing minors with algorithmically optimized "addictive feeds."
+*   **⏰ Notification Limits:** Restricting push notifications during specific nighttime hours without explicit parental consent.
+Last year, a similar bill stalled over constitutionality and privacy concerns. That conflict remains the central tension today:
+| Proponents (Lawmakers, Advocates) | Opponents (Tech Industry, TechNet) |
+| :--- | :--- |
+| **Focus:** Regulating the *delivery* mechanism, not the *access* to speech. | **Focus:** First Amendment infringement and limiting design choices. |
+| **Argument:** Necessary protection; citing former tech insiders (ex-Meta execs) who highlight prioritizing engagement over safety. | **Argument:** Parents should maintain primary judgment; the bill is overly restrictive and infringes on platform innovation. |
+### The Legal Precedent
+A crucial element supporting the bill's constitutionality is its model, based on a similar California law that has successfully withstood court challenges. Proponents argue this precedent validates the distinction: regulating the method of content delivery (addictive algorithms) does not equate to regulating the content itself.
+The question for platform design and policy leaders remains: When does optimizing for engagement cross the line into endangering well-being, and is state legislation the appropriate mechanism to draw that boundary?
+**#TechPolicy #SocialMediaRegulation #YouthSafety #HB1834 #AlgorithmicRegulation**
+***
+**What is your take?** Should lawmakers prioritize youth protection even if it risks legal challenges regarding free speech and platform design choices? Join the discussion below. 👇</t>
+  </si>
+  <si>
+    <t>https://www.geekwire.com/2026/amazon-confirms-16000-more-job-cuts-bringing-total-layoffs-to-30000-since-october/</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,97 +172,29 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -421,164 +460,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Agent_1</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Agent_2</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Processed</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.geekwire.com/2026/tech-moves-microsoft-cvp-jumps-to-google-seattle-engineers-launch-new-startup-github-names-vp/</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The article "Tech Moves: Microsoft CVP jumps to Google; Seattle engineers launch new startup; GitHub names VP" highlights several significant personnel changes and new ventures in the Pacific Northwest tech community. Satish Thomas, a 20-year Microsoft veteran and corporate vice president, has moved to Google, emphasizing the current AI era's impact on tech. Raji Rajagopalan has been appointed as GitHub's vice president of engineering, aiming to foster innovation and human-agent workflows in AI-driven development. Katie Bardaro joined Avante, a Seattle startup focused on HR administration and AI-powered benefits guidance, as senior VP of customer experience. A new stealthy startup focused on AI and the workplace has been launched by Vivek Sharma, along with collaborators Tore Hanssen, Robert Masson, and Calvin Grunewald. Additionally, Jeff Carr is now CEO of Atana, a startup specializing in behavior-based workplace training. Larry Hyrb, known as "Major Nelson" from his time at Microsoft Xbox, was laid off from Unity. Jay Bartot joined TheFounderVC as a technical advisor and chief technologist. Auger, a logistics and supply chain software startup, named Tucker Reimer as principal of supply chain innovation. Finally, Lucas Dickey joined Stripe as a product builder for Stripe Atlas.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>✨ PNW Tech Talent Watch: AI Fuels Executive Migration &amp; Startup Formation ✨
-The Pacific Northwest tech community is experiencing a massive talent liquidity event, driven overwhelmingly by the pursuit of cutting-edge AI opportunities. The recent shifts confirm that leaders are making big moves to shape the next era of development.
-Here is a quick breakdown of the significant transitions, illustrating where the industry is placing its bets:
-**➡️ Executive Migration Driven by AI:**
-*   **Microsoft to Google:** Satish Thomas, a 20-year Microsoft veteran and Corporate VP, has jumped to Google. This high-profile move underscores how the fierce competition in the AI space is drawing top-tier talent across legacy lines.
-*   **New Leadership at GitHub:** Raji Rajagopalan steps in as VP of Engineering, specifically tasked with innovating **human-agent workflows**—a clear strategic commitment to the future of AI-driven developer tools.
-**🚀 The Seattle Startup Boom:**
-*   A wave of new ventures is forming, focusing on highly specific, AI-enabled solutions:
-    *   **Stealth Mode AI:** Vivek Sharma, alongside Tore Hanssen, Robert Masson, and Calvin Grunewald, launched a secretive new startup focused on AI and the workplace.
-    *   **HR Tech Growth:** Avante brought on Katie Bardaro as SVP to scale its AI-powered benefits guidance and HR administration platform.
-    *   **Workplace Training Focus:** Jeff Carr is now CEO of Atana, specializing in behavior-based workplace training.
-**🔄 Strategic Moves &amp; Layoff Realities:**
-*   **The Founder's Journey:** Jay Bartot joined TheFounderVC as a Technical Advisor and Chief Technologist, signaling more seasoned experts are entering the venture capital ecosystem.
-*   **Product Building:** Lucas Dickey moved to Stripe as a Product Builder for Stripe Atlas, helping founders launch quickly.
-*   **Industry Flux:** Larry Hyrb ("Major Nelson" from Xbox fame) was laid off from Unity, a reminder that even high-profile roles face turbulence amid industry restructuring.
-**The Takeaway:**
-The theme is clear: Talent is flowing rapidly toward greenfield opportunities in AI infrastructure, developer tooling, and specialized workplace applications. The PNW is currently the epicenter for talent ready to exit large corporations to pursue these high-growth, foundational challenges.
-What do you think these migrations signal for the balance of power between Big Tech and emerging startups over the next year?
-#AIEra #TechMoves #SeattleTech #TalentWar #ExecutiveLeadership #StartupEcosystem #GitHub #Microsoft #Google #VentureCapital</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.geekwire.com/2026/vega-cloud-enters-receivership-with-millions-in-debt-in-surprise-turn-for-spokane-tech-standout/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-The Spokane-area tech startup, Vega Cloud, which develops software for managing cloud spending, has entered receivership due to its inability to pay debts, including nearly $830,000 owed to Amazon Web Services. The company, founded in 2018, had raised $12.2 million and achieved approximately $7 million in annual revenue by 2023. At the time of receivership, Vega Cloud had less than $17,000 in the bank and its workforce had decreased from about 65 employees two years ago to around 35. Receivership, a state-level process, places a neutral party in charge to manage assets, pause creditor collections, and supervise asset sales and payments. The largest secured creditor is Sun Mountain Private Credit Fund I, which is owed $3.5 million, backed by Vega Cloud's intellectual property.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>🚨 **A Stark Reminder: The Anatomy of a Tech Startup Receivership** 🚨
-The news concerning Spokane-based Vega Cloud, a startup specializing in cloud spending management, serves as a critical case study in the harsh reality of liquidity and debt management, even for companies showing strong revenue growth.
-Despite raising $12.2 million and achieving approximately $7 million in annual recurring revenue (ARR) by 2023, Vega Cloud has entered state-level receivership.
-Here is a factual breakdown of the situation, highlighting key operational and financial stress points:
----
-### **Vega Cloud: The Financial Reality Check**
-| Metric | Details | Analysis |
-| :--- | :--- | :--- |
-| **Funding &amp; Revenue** | $12.2M raised; $7M ARR in 2023. | Achieved significant traction and scale. |
-| **Liquidity Crisis** | Less than $17,000 cash in the bank at filing. | Major disconnect between revenue growth and working capital. |
-| **Key Operational Debt** | Nearly $830,000 owed to Amazon Web Services (AWS). | Ironic for a company selling cloud management tools; highlights the danger of large infrastructure bills. |
-| **Secured Debt** | $3.5 million owed to Sun Mountain Private Credit Fund I. | This debt is secured by the company's Intellectual Property (IP). |
-| **Operational Decline** | Workforce reduced from ~65 employees to ~35. | Indicates severe cost-cutting measures prior to the final filing. |
-### **What Receivership Means**
-Receivership places a neutral, court-appointed party in charge of the company's assets. Its primary function is to pause creditor collections and supervise the management, sale, and distribution of assets, ultimately maximizing returns for creditors.
-### **The Takeaway for Founders &amp; Investors**
-This situation underscores a vital lesson: **Revenue is vanity; cash is sanity.** Even $7M in ARR cannot protect a company if unit economics are unstable and working capital is mismanaged. Managing the cost of goods sold (COGS)—especially major cloud infrastructure—is paramount to survival.
-A difficult but necessary reminder that growth at all costs without tight financial controls is unsustainable.
-#TechFinance #Startups #Receivership #VentureCapital #CloudCosts #FinOps #LiquidityCrisis</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.geekwire.com/2026/washington-lawmakers-target-addictive-social-media-feeds-in-revived-push-for-youth-safeguards/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Washington lawmakers are renewing efforts to pass legislation aimed at protecting youth from "addictive feeds" on social media platforms. House Bill 1834, supported by state Attorney General Nick Brown and Governor Bob Ferguson, seeks to prevent companies like Instagram and TikTok from providing addictive feeds to minors and restrict push notifications during certain hours without parental consent. This renewed push comes after a similar bill stalled last year due to constitutionality and privacy concerns. The tech industry, represented by groups like TechNet and NetChoice, opposes the bill, arguing it infringes on the First Amendment and that parental judgment should be prioritized. However, advocates, including former tech executives like Kelly Stonelake, who previously worked at Meta, emphasize the necessity of such regulations, citing internal knowledge of companies prioritizing engagement over youth well-being. The bill is modeled after a California law that has withstood court challenges, and proponents assert it doesn't limit access to speech but rather the addictive delivery of it.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>💡 **The Battle for the Algorithm: Washington State Renews Push to Protect Youth from 'Addictive Feeds'**
-The debate over social media regulation is intensifying in Washington State as lawmakers revive efforts to pass House Bill 1834. This legislation, championed by Governor Bob Ferguson and Attorney General Nick Brown, aims to impose strict limits on how social media companies deliver content to minors, signaling a potential shift in platform accountability.
-This isn't just about limiting screen time; it's about regulating the core mechanisms of addiction built into the platforms themselves.
-### HB 1834: Key Provisions &amp; Conflict Points
-The proposed bill directly targets practices critics argue prioritize engagement metrics over youth well-being:
-*   **🚫 Banning Addictive Feeds:** Prohibiting platforms like Instagram and TikTok from providing minors with algorithmically optimized "addictive feeds."
-*   **⏰ Notification Limits:** Restricting push notifications during specific nighttime hours without explicit parental consent.
-Last year, a similar bill stalled over constitutionality and privacy concerns. That conflict remains the central tension today:
-| Proponents (Lawmakers, Advocates) | Opponents (Tech Industry, TechNet) |
-| :--- | :--- |
-| **Focus:** Regulating the *delivery* mechanism, not the *access* to speech. | **Focus:** First Amendment infringement and limiting design choices. |
-| **Argument:** Necessary protection; citing former tech insiders (ex-Meta execs) who highlight prioritizing engagement over safety. | **Argument:** Parents should maintain primary judgment; the bill is overly restrictive and infringes on platform innovation. |
-### The Legal Precedent
-A crucial element supporting the bill's constitutionality is its model, based on a similar California law that has successfully withstood court challenges. Proponents argue this precedent validates the distinction: regulating the method of content delivery (addictive algorithms) does not equate to regulating the content itself.
-The question for platform design and policy leaders remains: When does optimizing for engagement cross the line into endangering well-being, and is state legislation the appropriate mechanism to draw that boundary?
-**#TechPolicy #SocialMediaRegulation #YouthSafety #HB1834 #AlgorithmicRegulation**
-***
-**What is your take?** Should lawmakers prioritize youth protection even if it risks legal challenges regarding free speech and platform design choices? Join the discussion below. 👇</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/articles.xlsx
+++ b/data/articles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\LinkedinSummaryBot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B181B5E2-924D-4AA8-BC9A-6FC37BEF1550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB46C0DF-2351-4B63-93FD-A29A4C584F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>URL</t>
   </si>
@@ -32,94 +32,6 @@
   </si>
   <si>
     <t>Processed</t>
-  </si>
-  <si>
-    <t>https://www.geekwire.com/2026/tech-moves-microsoft-cvp-jumps-to-google-seattle-engineers-launch-new-startup-github-names-vp/</t>
-  </si>
-  <si>
-    <t>The article "Tech Moves: Microsoft CVP jumps to Google; Seattle engineers launch new startup; GitHub names VP" highlights several significant personnel changes and new ventures in the Pacific Northwest tech community. Satish Thomas, a 20-year Microsoft veteran and corporate vice president, has moved to Google, emphasizing the current AI era's impact on tech. Raji Rajagopalan has been appointed as GitHub's vice president of engineering, aiming to foster innovation and human-agent workflows in AI-driven development. Katie Bardaro joined Avante, a Seattle startup focused on HR administration and AI-powered benefits guidance, as senior VP of customer experience. A new stealthy startup focused on AI and the workplace has been launched by Vivek Sharma, along with collaborators Tore Hanssen, Robert Masson, and Calvin Grunewald. Additionally, Jeff Carr is now CEO of Atana, a startup specializing in behavior-based workplace training. Larry Hyrb, known as "Major Nelson" from his time at Microsoft Xbox, was laid off from Unity. Jay Bartot joined TheFounderVC as a technical advisor and chief technologist. Auger, a logistics and supply chain software startup, named Tucker Reimer as principal of supply chain innovation. Finally, Lucas Dickey joined Stripe as a product builder for Stripe Atlas.</t>
-  </si>
-  <si>
-    <t>✨ PNW Tech Talent Watch: AI Fuels Executive Migration &amp; Startup Formation ✨
-The Pacific Northwest tech community is experiencing a massive talent liquidity event, driven overwhelmingly by the pursuit of cutting-edge AI opportunities. The recent shifts confirm that leaders are making big moves to shape the next era of development.
-Here is a quick breakdown of the significant transitions, illustrating where the industry is placing its bets:
-**➡️ Executive Migration Driven by AI:**
-*   **Microsoft to Google:** Satish Thomas, a 20-year Microsoft veteran and Corporate VP, has jumped to Google. This high-profile move underscores how the fierce competition in the AI space is drawing top-tier talent across legacy lines.
-*   **New Leadership at GitHub:** Raji Rajagopalan steps in as VP of Engineering, specifically tasked with innovating **human-agent workflows**—a clear strategic commitment to the future of AI-driven developer tools.
-**🚀 The Seattle Startup Boom:**
-*   A wave of new ventures is forming, focusing on highly specific, AI-enabled solutions:
-    *   **Stealth Mode AI:** Vivek Sharma, alongside Tore Hanssen, Robert Masson, and Calvin Grunewald, launched a secretive new startup focused on AI and the workplace.
-    *   **HR Tech Growth:** Avante brought on Katie Bardaro as SVP to scale its AI-powered benefits guidance and HR administration platform.
-    *   **Workplace Training Focus:** Jeff Carr is now CEO of Atana, specializing in behavior-based workplace training.
-**🔄 Strategic Moves &amp; Layoff Realities:**
-*   **The Founder's Journey:** Jay Bartot joined TheFounderVC as a Technical Advisor and Chief Technologist, signaling more seasoned experts are entering the venture capital ecosystem.
-*   **Product Building:** Lucas Dickey moved to Stripe as a Product Builder for Stripe Atlas, helping founders launch quickly.
-*   **Industry Flux:** Larry Hyrb ("Major Nelson" from Xbox fame) was laid off from Unity, a reminder that even high-profile roles face turbulence amid industry restructuring.
-**The Takeaway:**
-The theme is clear: Talent is flowing rapidly toward greenfield opportunities in AI infrastructure, developer tooling, and specialized workplace applications. The PNW is currently the epicenter for talent ready to exit large corporations to pursue these high-growth, foundational challenges.
-What do you think these migrations signal for the balance of power between Big Tech and emerging startups over the next year?
-#AIEra #TechMoves #SeattleTech #TalentWar #ExecutiveLeadership #StartupEcosystem #GitHub #Microsoft #Google #VentureCapital</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>https://www.geekwire.com/2026/vega-cloud-enters-receivership-with-millions-in-debt-in-surprise-turn-for-spokane-tech-standout/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-The Spokane-area tech startup, Vega Cloud, which develops software for managing cloud spending, has entered receivership due to its inability to pay debts, including nearly $830,000 owed to Amazon Web Services. The company, founded in 2018, had raised $12.2 million and achieved approximately $7 million in annual revenue by 2023. At the time of receivership, Vega Cloud had less than $17,000 in the bank and its workforce had decreased from about 65 employees two years ago to around 35. Receivership, a state-level process, places a neutral party in charge to manage assets, pause creditor collections, and supervise asset sales and payments. The largest secured creditor is Sun Mountain Private Credit Fund I, which is owed $3.5 million, backed by Vega Cloud's intellectual property.</t>
-  </si>
-  <si>
-    <t>🚨 **A Stark Reminder: The Anatomy of a Tech Startup Receivership** 🚨
-The news concerning Spokane-based Vega Cloud, a startup specializing in cloud spending management, serves as a critical case study in the harsh reality of liquidity and debt management, even for companies showing strong revenue growth.
-Despite raising $12.2 million and achieving approximately $7 million in annual recurring revenue (ARR) by 2023, Vega Cloud has entered state-level receivership.
-Here is a factual breakdown of the situation, highlighting key operational and financial stress points:
----
-### **Vega Cloud: The Financial Reality Check**
-| Metric | Details | Analysis |
-| :--- | :--- | :--- |
-| **Funding &amp; Revenue** | $12.2M raised; $7M ARR in 2023. | Achieved significant traction and scale. |
-| **Liquidity Crisis** | Less than $17,000 cash in the bank at filing. | Major disconnect between revenue growth and working capital. |
-| **Key Operational Debt** | Nearly $830,000 owed to Amazon Web Services (AWS). | Ironic for a company selling cloud management tools; highlights the danger of large infrastructure bills. |
-| **Secured Debt** | $3.5 million owed to Sun Mountain Private Credit Fund I. | This debt is secured by the company's Intellectual Property (IP). |
-| **Operational Decline** | Workforce reduced from ~65 employees to ~35. | Indicates severe cost-cutting measures prior to the final filing. |
-### **What Receivership Means**
-Receivership places a neutral, court-appointed party in charge of the company's assets. Its primary function is to pause creditor collections and supervise the management, sale, and distribution of assets, ultimately maximizing returns for creditors.
-### **The Takeaway for Founders &amp; Investors**
-This situation underscores a vital lesson: **Revenue is vanity; cash is sanity.** Even $7M in ARR cannot protect a company if unit economics are unstable and working capital is mismanaged. Managing the cost of goods sold (COGS)—especially major cloud infrastructure—is paramount to survival.
-A difficult but necessary reminder that growth at all costs without tight financial controls is unsustainable.
-#TechFinance #Startups #Receivership #VentureCapital #CloudCosts #FinOps #LiquidityCrisis</t>
-  </si>
-  <si>
-    <t>https://www.geekwire.com/2026/washington-lawmakers-target-addictive-social-media-feeds-in-revived-push-for-youth-safeguards/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Washington lawmakers are renewing efforts to pass legislation aimed at protecting youth from "addictive feeds" on social media platforms. House Bill 1834, supported by state Attorney General Nick Brown and Governor Bob Ferguson, seeks to prevent companies like Instagram and TikTok from providing addictive feeds to minors and restrict push notifications during certain hours without parental consent. This renewed push comes after a similar bill stalled last year due to constitutionality and privacy concerns. The tech industry, represented by groups like TechNet and NetChoice, opposes the bill, arguing it infringes on the First Amendment and that parental judgment should be prioritized. However, advocates, including former tech executives like Kelly Stonelake, who previously worked at Meta, emphasize the necessity of such regulations, citing internal knowledge of companies prioritizing engagement over youth well-being. The bill is modeled after a California law that has withstood court challenges, and proponents assert it doesn't limit access to speech but rather the addictive delivery of it.</t>
-  </si>
-  <si>
-    <t>💡 **The Battle for the Algorithm: Washington State Renews Push to Protect Youth from 'Addictive Feeds'**
-The debate over social media regulation is intensifying in Washington State as lawmakers revive efforts to pass House Bill 1834. This legislation, championed by Governor Bob Ferguson and Attorney General Nick Brown, aims to impose strict limits on how social media companies deliver content to minors, signaling a potential shift in platform accountability.
-This isn't just about limiting screen time; it's about regulating the core mechanisms of addiction built into the platforms themselves.
-### HB 1834: Key Provisions &amp; Conflict Points
-The proposed bill directly targets practices critics argue prioritize engagement metrics over youth well-being:
-*   **🚫 Banning Addictive Feeds:** Prohibiting platforms like Instagram and TikTok from providing minors with algorithmically optimized "addictive feeds."
-*   **⏰ Notification Limits:** Restricting push notifications during specific nighttime hours without explicit parental consent.
-Last year, a similar bill stalled over constitutionality and privacy concerns. That conflict remains the central tension today:
-| Proponents (Lawmakers, Advocates) | Opponents (Tech Industry, TechNet) |
-| :--- | :--- |
-| **Focus:** Regulating the *delivery* mechanism, not the *access* to speech. | **Focus:** First Amendment infringement and limiting design choices. |
-| **Argument:** Necessary protection; citing former tech insiders (ex-Meta execs) who highlight prioritizing engagement over safety. | **Argument:** Parents should maintain primary judgment; the bill is overly restrictive and infringes on platform innovation. |
-### The Legal Precedent
-A crucial element supporting the bill's constitutionality is its model, based on a similar California law that has successfully withstood court challenges. Proponents argue this precedent validates the distinction: regulating the method of content delivery (addictive algorithms) does not equate to regulating the content itself.
-The question for platform design and policy leaders remains: When does optimizing for engagement cross the line into endangering well-being, and is state legislation the appropriate mechanism to draw that boundary?
-**#TechPolicy #SocialMediaRegulation #YouthSafety #HB1834 #AlgorithmicRegulation**
-***
-**What is your take?** Should lawmakers prioritize youth protection even if it risks legal challenges regarding free speech and platform design choices? Join the discussion below. 👇</t>
-  </si>
-  <si>
-    <t>https://www.geekwire.com/2026/amazon-confirms-16000-more-job-cuts-bringing-total-layoffs-to-30000-since-october/</t>
   </si>
 </sst>
 </file>
@@ -176,9 +88,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -482,57 +397,15 @@
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
